--- a/artfynd/A 58512-2019 artfynd.xlsx
+++ b/artfynd/A 58512-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58512-2019 artfynd.xlsx
+++ b/artfynd/A 58512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79087787</v>
+        <v>79087762</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>77588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607524.8407301455</v>
+        <v>607588.6245488432</v>
       </c>
       <c r="R2" t="n">
-        <v>7275130.787569438</v>
+        <v>7275077.225803371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79087818</v>
+        <v>79087769</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
+        <v>78603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607511.8942458994</v>
+        <v>607588.6245488432</v>
       </c>
       <c r="R3" t="n">
-        <v>7275155.57796421</v>
+        <v>7275077.225803371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79087802</v>
+        <v>79087787</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1008,7 +1009,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79087805</v>
+        <v>79087818</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
+        <v>81236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607524.8407301455</v>
+        <v>607511.8942458994</v>
       </c>
       <c r="R5" t="n">
-        <v>7275130.787569438</v>
+        <v>7275155.57796421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75913103</v>
+        <v>79087802</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,41 +1159,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gajbienåjvvie, Ly lm</t>
+          <t>Njuöniesvarie, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607543.1255325245</v>
+        <v>607524.8407301455</v>
       </c>
       <c r="R6" t="n">
-        <v>7275062.695983796</v>
+        <v>7275130.787569438</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1216,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-08-07</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1227,7 +1226,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-08-07</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1235,39 +1234,35 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack, "ringade träd"</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79087826</v>
+        <v>79087805</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
+        <v>77588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607511.8942458994</v>
+        <v>607524.8407301455</v>
       </c>
       <c r="R7" t="n">
-        <v>7275155.57796421</v>
+        <v>7275130.787569438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79087808</v>
+        <v>75913103</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
+        <v>56395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,44 +1387,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Njuöniesvarie, Ly lm</t>
+          <t>Gajbienåjvvie, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607524.8407301455</v>
+        <v>607543.1255325245</v>
       </c>
       <c r="R8" t="n">
-        <v>7275130.787569438</v>
+        <v>7275062.695983796</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1449,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
+          <t>2017-08-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1463,7 +1459,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
+          <t>2017-08-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1471,35 +1467,39 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack, "ringade träd"</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79087821</v>
+        <v>79087826</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,27 +1512,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1594,6 +1593,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79087769</v>
+        <v>79087808</v>
       </c>
       <c r="B10" t="n">
-        <v>78603</v>
+        <v>89356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607588.6245488432</v>
+        <v>607524.8407301455</v>
       </c>
       <c r="R10" t="n">
-        <v>7275077.225803371</v>
+        <v>7275130.787569438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79087727</v>
+        <v>79087821</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
+        <v>56395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,26 +1744,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1771,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607624.612547453</v>
+        <v>607511.8942458994</v>
       </c>
       <c r="R11" t="n">
-        <v>7275079.803660583</v>
+        <v>7275155.57796421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1826,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79087737</v>
+        <v>79087727</v>
       </c>
       <c r="B12" t="n">
-        <v>96354</v>
+        <v>89673</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,31 +1856,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1961,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79087708</v>
+        <v>79087737</v>
       </c>
       <c r="B13" t="n">
-        <v>89406</v>
+        <v>96354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,30 +1972,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607629.9963840802</v>
+        <v>607624.612547453</v>
       </c>
       <c r="R13" t="n">
-        <v>7275102.374302789</v>
+        <v>7275079.803660583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79087762</v>
+        <v>79087708</v>
       </c>
       <c r="B14" t="n">
-        <v>77588</v>
+        <v>89406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607588.6245488432</v>
+        <v>607629.9963840802</v>
       </c>
       <c r="R14" t="n">
-        <v>7275077.225803371</v>
+        <v>7275102.374302789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
